--- a/salidas/reportes/reporte_completo.xlsx
+++ b/salidas/reportes/reporte_completo.xlsx
@@ -551,7 +551,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>La decisión se elige por robustez (3.000 escenarios) y se identifican 16 datos que podrían cambiarla.</t>
+          <t>La decisión se elige por robustez (3.000 escenarios) y se identifican 15 datos que podrían cambiarla.</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -3719,8 +3719,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50.4" customWidth="1" min="1" max="1"/>
-    <col width="13.5" customWidth="1" min="2" max="2"/>
-    <col width="27.9" customWidth="1" min="3" max="3"/>
+    <col width="16.2" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4092,11 +4092,11 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.5</v>
+        <v>0.2367586007137318</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>valor de referencia (parámetro)</t>
+          <t>estimado desde histórico (n=3 registros)</t>
         </is>
       </c>
     </row>
@@ -5007,11 +5007,11 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>0.5</v>
+        <v>0.8015396840445483</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>valor de referencia (parámetro)</t>
+          <t>estimado desde histórico (n=8 registros)</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Puntaje 0.539 (puesto 9 de 26 alternativas que compiten) · Necesidad 0.50 · Brecha CA 0.44 · Evidencia 0.83 · Cobertura 1.00 · Cobeneficios 0.00 · La medida aparece en el 71% de los 3.000 escenarios simulados; confianza Alta · Si se elimina, el modelo la reemplaza por: M05-MAR, M07-GUA, M07-RIO.</t>
+          <t>Puntaje 0.542 (puesto 8 de 26 alternativas que compiten) · Necesidad 0.51 · Brecha CA 0.44 · Evidencia 0.83 · Cobertura 1.00 · Cobeneficios 0.00 · La medida aparece en el 71% de los 3.000 escenarios simulados; confianza Alta · Si se elimina, el modelo la reemplaza por: M05-MAR, M07-GUA, M07-RIO.</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Puntaje 0.628 (puesto 1 de 26 alternativas que compiten) · Necesidad 0.75 · Brecha CA 0.39 · Evidencia 1.00 · Cobertura 0.33 · Cobeneficios 0.67 · La medida aparece en el 27% de los 3.000 escenarios simulados; confianza Media · Si se elimina, el modelo la reemplaza por: M05-GUA, M05-MAR.</t>
+          <t>Puntaje 0.628 (puesto 1 de 26 alternativas que compiten) · Necesidad 0.75 · Brecha CA 0.39 · Evidencia 1.00 · Cobertura 0.33 · Cobeneficios 0.67 · La medida aparece en el 27% de los 3.000 escenarios simulados; confianza Media · Si se elimina, el modelo la reemplaza por: M05-MAR, M13-COR.</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Puntaje 0.525 (puesto 10 de 26 alternativas que compiten) · Necesidad 0.50 · Brecha CA 0.25 · Evidencia 1.00 · Cobertura 0.33 · Cobeneficios 0.67 · La medida aparece en el 79% de los 3.000 escenarios simulados; confianza Media · Si se elimina, el modelo la reemplaza por: M07-GUA.</t>
+          <t>Puntaje 0.525 (puesto 11 de 26 alternativas que compiten) · Necesidad 0.50 · Brecha CA 0.25 · Evidencia 1.00 · Cobertura 0.33 · Cobeneficios 0.67 · La medida aparece en el 79% de los 3.000 escenarios simulados; confianza Media · Si se elimina, el modelo la reemplaza por: M07-GUA.</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -7152,7 +7152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.3" customWidth="1" min="1" max="1"/>
@@ -7369,12 +7369,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Resultado si se cruza el umbral: M03-COR + M05-GUA + M05-MAR + M07-MAR + M14-COR</t>
+          <t>Resultado si se cruza el umbral: M01-RIO + M03-COR + M05-GUA + M13-COR + M14-COR</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>cambia QUÉ medidas si ≤ 0.09</t>
+          <t>cambia QUÉ medidas si ≤ 0.12</t>
         </is>
       </c>
     </row>
@@ -7396,12 +7396,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Resultado si se cruza el umbral: M03-COR + M05-GUA + M05-MAR + M07-MAR + M14-COR</t>
+          <t>Resultado si se cruza el umbral: M01-RIO + M03-COR + M05-GUA + M13-COR + M14-COR</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>cambia QUÉ medidas si ≥ 0.67</t>
+          <t>cambia QUÉ medidas si ≥ 0.66</t>
         </is>
       </c>
     </row>
@@ -7428,7 +7428,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>cambia QUÉ medidas si ≥ 0.93</t>
+          <t>cambia QUÉ medidas si ≥ 0.63</t>
         </is>
       </c>
     </row>
@@ -7504,12 +7504,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Resultado si se cruza el umbral: M03-COR + M05-RIO + M05-MAR + M07-MAR + M14-COR</t>
+          <t>Resultado si se cruza el umbral: M01-RIO + M03-COR + M05-MAR + M13-COR + M14-COR</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>cambia QUÉ medidas si ≤ 0.09</t>
+          <t>cambia QUÉ medidas si ≤ 0.12</t>
         </is>
       </c>
     </row>
@@ -7531,12 +7531,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Resultado si se cruza el umbral: M03-COR + M05-RIO + M05-MAR + M07-MAR + M14-COR</t>
+          <t>Resultado si se cruza el umbral: M01-RIO + M03-COR + M05-MAR + M13-COR + M14-COR</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>cambia QUÉ medidas si ≥ 0.67</t>
+          <t>cambia QUÉ medidas si ≥ 0.66</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>cambia QUÉ medidas si ≥ 0.93</t>
+          <t>cambia QUÉ medidas si ≥ 0.90</t>
         </is>
       </c>
     </row>
@@ -7639,12 +7639,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Resultado si se cruza el umbral: M03-COR + M05-RIO + M05-MAR + M07-MAR + M14-COR</t>
+          <t>Resultado si se cruza el umbral: M01-RIO + M03-COR + M05-RIO + M13-COR + M14-COR</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>cambia QUÉ medidas si ≤ 0.09</t>
+          <t>cambia QUÉ medidas si ≤ 0.12</t>
         </is>
       </c>
     </row>
@@ -7666,12 +7666,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Resultado si se cruza el umbral: M03-COR + M05-RIO + M05-MAR + M07-MAR + M14-COR</t>
+          <t>Resultado si se cruza el umbral: M01-RIO + M03-COR + M05-RIO + M13-COR + M14-COR</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>cambia QUÉ medidas si ≥ 0.67</t>
+          <t>cambia QUÉ medidas si ≥ 0.66</t>
         </is>
       </c>
     </row>
@@ -7683,7 +7683,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Rionegro · Riesgo de desastres · Vulnerabilidad</t>
+          <t>Rionegro · Seguridad alimentaria · Capacidad adaptativa</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -7693,12 +7693,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Resultado si se cruza el umbral: M01-RIO + M03-COR + M05-MAR + M13-COR + M14-COR</t>
+          <t>Resultado si se cruza el umbral: M01-RIO + M02-RIO + M03-COR + M07-RIO + M14-COR</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>cambia QUÉ medidas si ≥ 0.93</t>
+          <t>cambia DÓNDE si ≤ 0.49</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Rionegro · Seguridad alimentaria · Capacidad adaptativa</t>
+          <t>Rionegro · Seguridad alimentaria · Vulnerabilidad</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -7725,19 +7725,19 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>cambia DÓNDE si ≤ 0.49</t>
+          <t>cambia DÓNDE si ≥ 0.51</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Dato que cambia la decisión</t>
+          <t>Dependencias (Reto sec. 5)</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Rionegro · Seguridad alimentaria · Vulnerabilidad</t>
+          <t>Empresa ACV → captación o fuente hídrica, caudal concesionado vs usado</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Resultado si se cruza el umbral: M01-RIO + M02-RIO + M03-COR + M07-RIO + M14-COR</t>
+          <t>Sin esto no se puede priorizar 'Uso intersectorial eficiente del agua' (M04)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>cambia DÓNDE si ≥ 0.51</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7764,7 +7764,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Empresa ACV → captación o fuente hídrica, caudal concesionado vs usado</t>
+          <t>Empresa ACV → vía de acceso crítica, circuito eléctrico, proveedores críticos de la región, trabajadores por municipio</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Sin esto no se puede priorizar 'Uso intersectorial eficiente del agua' (M04)</t>
+          <t>Sin esto no se puede priorizar infraestructura (M11, M12) ni saber qué interrupción se propaga</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Empresa ACV → vía de acceso crítica, circuito eléctrico, proveedores críticos de la región, trabajadores por municipio</t>
+          <t>Punto crítico de vía o servicio → población y empresas que dependen, rutas alternas, tiempo tolerable de interrupción</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Sin esto no se puede priorizar infraestructura (M11, M12) ni saber qué interrupción se propaga</t>
+          <t>Define dónde una obra de infraestructura protege más</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -7813,12 +7813,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Dependencias (Reto sec. 5)</t>
+          <t>Efectividad</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Punto crítico de vía o servicio → población y empresas que dependen, rutas alternas, tiempo tolerable de interrupción</t>
+          <t>Línea base y medición posterior del indicador de resultado de cada medida</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Define dónde una obra de infraestructura protege más</t>
+          <t>Permitiría estimar efectividad (hoy α se prueba de 0 a 1) y, a futuro, entrenar un modelo de aprendizaje automático</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -7840,12 +7840,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Efectividad</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Línea base y medición posterior del indicador de resultado de cada medida</t>
+          <t>Vigilancia de enfermedades climato-sensibles por municipio</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Permitiría estimar efectividad (hoy α se prueba de 0 a 1) y, a futuro, entrenar un modelo de aprendizaje automático</t>
+          <t>La medida de salud (M15) no compite por falta de datos</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -7867,52 +7867,25 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Registro histórico</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Vigilancia de enfermedades climato-sensibles por municipio</t>
+          <t>Medidas de adaptación de Marinilla (1 registro 2018–2025)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Incompleto</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>La medida de salud (M15) no compite por falta de datos</t>
+          <t>Subregistro: no indica menor necesidad</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Registro histórico</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Medidas de adaptación de Marinilla (1 registro 2018–2025)</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Incompleto</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Subregistro: no indica menor necesidad</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8176,7 +8149,7 @@
         <v>0.174</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.373</v>
+        <v>0.369</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0.41</v>
@@ -8282,7 +8255,7 @@
         <v>0.901</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.953</v>
+        <v>0.952</v>
       </c>
       <c r="V3" s="2" t="n">
         <v>1</v>
@@ -8391,7 +8364,7 @@
         <v>0.614</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.437</v>
+        <v>0.443</v>
       </c>
       <c r="W4" s="2" t="n">
         <v>0.285</v>
@@ -8452,7 +8425,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.513</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>0.443</v>
@@ -8476,10 +8449,10 @@
         <v>1</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.5387</v>
+        <v>0.5425</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.5707</v>
+        <v>0.5735</v>
       </c>
       <c r="Q5" s="2" t="b">
         <v>1</v>
@@ -8494,10 +8467,10 @@
         <v>0.821</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.921</v>
+        <v>0.927</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.911</v>
+        <v>0.918</v>
       </c>
       <c r="W5" s="2" t="n">
         <v>0.712</v>
@@ -8596,10 +8569,10 @@
         <v>0.374</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.674</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.729</v>
+        <v>0.732</v>
       </c>
       <c r="W6" s="2" t="n">
         <v>0.381</v>
@@ -8702,7 +8675,7 @@
         <v>0.271</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.17</v>
+        <v>0.171</v>
       </c>
       <c r="V7" s="2" t="n">
         <v>0</v>
@@ -8914,10 +8887,10 @@
         <v>0.266</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.521</v>
+        <v>0.526</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.271</v>
+        <v>0.268</v>
       </c>
       <c r="W9" s="2" t="n">
         <v>0.263</v>
@@ -9023,7 +8996,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.089</v>
+        <v>0.082</v>
       </c>
       <c r="W10" s="2" t="n">
         <v>0.091</v>
@@ -9163,113 +9136,113 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>M07-RIO</t>
+          <t>M13-COR</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Protección y reconversión de suelos agrícolas estratégicos</t>
+          <t>Fortalecimiento de Sistemas de Alerta Temprana – SAT</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Seguridad alimentaria</t>
+          <t>Riesgo de desastres</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Rionegro</t>
+          <t>Corredor</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.5</v>
+        <v>0.513</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.25</v>
+        <v>0.443</v>
       </c>
       <c r="I12" s="2" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="J12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="K12" s="2" t="n">
         <v>0.333</v>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="L12" s="2" t="n">
         <v>0.667</v>
       </c>
-      <c r="L12" s="2" t="n">
-        <v>0.5</v>
-      </c>
       <c r="M12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N12" s="2" t="b">
         <v>1</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>0.525</v>
+        <v>0.5258</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>0.5187</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="Q12" s="2" t="b">
         <v>0</v>
       </c>
       <c r="R12" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" s="2" t="b">
         <v>0</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>0.341</v>
+        <v>0.192</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>0.141</v>
+        <v>0.366</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>0.408</v>
+        <v>0.256</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>0.347</v>
+        <v>0.181</v>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>No evaluable (sin dato 2060)</t>
+          <t>Se refuerza (riesgo sube a 2060)</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>Recurso hídrico; Riesgo de desastres</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t># de actores educados y capacitados en términos de conservación y uso del suelo anualmente</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>RELACIONADO (Excel: Protección de suelos)</t>
+          <t>NO DISPONIBLE</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>M07-GUA</t>
+          <t>M07-RIO</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -9284,7 +9257,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Guarne</t>
+          <t>Rionegro</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
@@ -9335,16 +9308,16 @@
         <v>0</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>0.355</v>
+        <v>0.341</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>0.102</v>
+        <v>0.134</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>0</v>
+        <v>0.404</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>0.36</v>
+        <v>0.347</v>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
@@ -9375,106 +9348,106 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>M13-COR</t>
+          <t>M07-GUA</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Fortalecimiento de Sistemas de Alerta Temprana – SAT</t>
+          <t>Protección y reconversión de suelos agrícolas estratégicos</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Riesgo de desastres</t>
+          <t>Seguridad alimentaria</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Corredor</t>
+          <t>Guarne</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.443</v>
+        <v>0.25</v>
       </c>
       <c r="I14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2" t="n">
         <v>0.333</v>
       </c>
-      <c r="J14" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K14" s="2" t="n">
-        <v>0.333</v>
+        <v>0.667</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N14" s="2" t="b">
         <v>1</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>0.522</v>
+        <v>0.525</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>0.5582</v>
+        <v>0.5187</v>
       </c>
       <c r="Q14" s="2" t="b">
         <v>0</v>
       </c>
       <c r="R14" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" s="2" t="b">
         <v>0</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>0.192</v>
+        <v>0.355</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>0.347</v>
+        <v>0.098</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>0.248</v>
+        <v>0</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>0.181</v>
+        <v>0.36</v>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>Se refuerza (riesgo sube a 2060)</t>
+          <t>No evaluable (sin dato 2060)</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Recurso hídrico; Riesgo de desastres</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t># de actores educados y capacitados en términos de conservación y uso del suelo anualmente</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>NO DISPONIBLE</t>
+          <t>RELACIONADO (Excel: Protección de suelos)</t>
         </is>
       </c>
     </row>
@@ -10186,10 +10159,10 @@
         <v>0.284</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>0.039</v>
+        <v>0.037</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>0.408</v>
+        <v>0.404</v>
       </c>
       <c r="W21" s="2" t="n">
         <v>0.314</v>
@@ -10292,10 +10265,10 @@
         <v>0.292</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>0.039</v>
+        <v>0.037</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>0.408</v>
+        <v>0.404</v>
       </c>
       <c r="W22" s="2" t="n">
         <v>0.325</v>
@@ -12221,12 +12194,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50.4" customWidth="1" min="1" max="1"/>
-    <col width="13.5" customWidth="1" min="2" max="2"/>
-    <col width="27.9" customWidth="1" min="3" max="3"/>
+    <col width="16.2" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="19.8" customWidth="1" min="6" max="6"/>
@@ -12318,13 +12291,13 @@
       </c>
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>M03-COR + M05-GUA + M05-MAR + M07-MAR + M14-COR</t>
+          <t>M01-RIO + M03-COR + M05-GUA + M13-COR + M14-COR</t>
         </is>
       </c>
     </row>
@@ -12343,14 +12316,14 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>M03-COR + M05-GUA + M05-MAR + M07-MAR + M14-COR</t>
+          <t>M01-RIO + M03-COR + M05-GUA + M13-COR + M14-COR</t>
         </is>
       </c>
     </row>
@@ -12361,15 +12334,15 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.2367586007137318</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>valor de referencia (parámetro)</t>
+          <t>estimado desde histórico (n=3 registros)</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.93</v>
+        <v>0.63</v>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
@@ -12452,13 +12425,13 @@
       </c>
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>M03-COR + M05-RIO + M05-MAR + M07-MAR + M14-COR</t>
+          <t>M01-RIO + M03-COR + M05-MAR + M13-COR + M14-COR</t>
         </is>
       </c>
     </row>
@@ -12477,14 +12450,14 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>M03-COR + M05-RIO + M05-MAR + M07-MAR + M14-COR</t>
+          <t>M01-RIO + M03-COR + M05-MAR + M13-COR + M14-COR</t>
         </is>
       </c>
     </row>
@@ -12503,7 +12476,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr"/>
@@ -12586,13 +12559,13 @@
       </c>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>M03-COR + M05-RIO + M05-MAR + M07-MAR + M14-COR</t>
+          <t>M01-RIO + M03-COR + M05-RIO + M13-COR + M14-COR</t>
         </is>
       </c>
     </row>
@@ -12611,21 +12584,21 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>M03-COR + M05-RIO + M05-MAR + M07-MAR + M14-COR</t>
+          <t>M01-RIO + M03-COR + M05-RIO + M13-COR + M14-COR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Rionegro · Riesgo de desastres · Vulnerabilidad</t>
+          <t>Rionegro · Seguridad alimentaria · Capacidad adaptativa</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -12636,22 +12609,22 @@
           <t>valor de referencia (parámetro)</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
-        <v>0.93</v>
-      </c>
+      <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="n">
+        <v>0.49</v>
+      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>M01-RIO + M03-COR + M05-MAR + M13-COR + M14-COR</t>
+          <t>M01-RIO + M02-RIO + M03-COR + M07-RIO + M14-COR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Rionegro · Seguridad alimentaria · Capacidad adaptativa</t>
+          <t>Rionegro · Seguridad alimentaria · Vulnerabilidad</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -12664,37 +12637,11 @@
       </c>
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="n">
-        <v>0.49</v>
-      </c>
+      <c r="F16" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>M01-RIO + M02-RIO + M03-COR + M07-RIO + M14-COR</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Rionegro · Seguridad alimentaria · Vulnerabilidad</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>valor de referencia (parámetro)</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>M01-RIO + M02-RIO + M03-COR + M07-RIO + M14-COR</t>
         </is>
@@ -12931,14 +12878,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>M03-COR + M05-GUA + M05-MAR + M07-MAR + M14-COR</t>
+          <t>M01-RIO + M03-COR + M05-MAR + M13-COR + M14-COR</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
     </row>
